--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
@@ -422,7 +422,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,12 +432,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,17 +482,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="121">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,25 +52,31 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Шумен 2</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Търговище</t>
-  </si>
-  <si>
-    <t>Бургас езеро</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1913 О5 Шумен 2</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1918 O5 Търговище</t>
+  </si>
+  <si>
+    <t>1152 Бургас езеро</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В8661КК</t>
@@ -88,13 +97,16 @@
     <t>В9037ВВ</t>
   </si>
   <si>
+    <t>В0452ВК</t>
+  </si>
+  <si>
+    <t>В0859ВМ</t>
+  </si>
+  <si>
     <t>В3106НР</t>
   </si>
   <si>
-    <t>В0859ВМ</t>
-  </si>
-  <si>
-    <t>В0452ВК</t>
+    <t>В2370ТК</t>
   </si>
   <si>
     <t>21СС</t>
@@ -103,12 +115,18 @@
     <t>В4303РА</t>
   </si>
   <si>
-    <t>В2370ТК</t>
-  </si>
-  <si>
     <t>В3675НМ</t>
   </si>
   <si>
+    <t>В0357НТ</t>
+  </si>
+  <si>
+    <t>В3188ТХ</t>
+  </si>
+  <si>
+    <t>В3104НР</t>
+  </si>
+  <si>
     <t>78970153027720464</t>
   </si>
   <si>
@@ -127,13 +145,16 @@
     <t>78970153027720506</t>
   </si>
   <si>
+    <t>78970153027720498</t>
+  </si>
+  <si>
+    <t>78970153027720357</t>
+  </si>
+  <si>
     <t>78970153027720373</t>
   </si>
   <si>
-    <t>78970153027720357</t>
-  </si>
-  <si>
-    <t>78970153027720498</t>
+    <t>78970153027720548</t>
   </si>
   <si>
     <t>78970153027720613</t>
@@ -142,12 +163,18 @@
     <t>78970153027720449</t>
   </si>
   <si>
-    <t>78970153027720548</t>
-  </si>
-  <si>
     <t>78970153027720480</t>
   </si>
   <si>
+    <t>78970153027720522</t>
+  </si>
+  <si>
+    <t>78970153027720415</t>
+  </si>
+  <si>
+    <t>78970153027720365</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
@@ -157,64 +184,181 @@
     <t>DIESEL DOUBLE FILTERED</t>
   </si>
   <si>
-    <t>2026-06-16 17:35:37</t>
-  </si>
-  <si>
-    <t>2026-06-17 13:54:43</t>
-  </si>
-  <si>
-    <t>2026-06-18 10:07:30</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:49:24</t>
-  </si>
-  <si>
-    <t>2026-06-19 10:51:32</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:45:59</t>
-  </si>
-  <si>
-    <t>2026-06-19 15:58:19</t>
-  </si>
-  <si>
-    <t>2026-06-20 10:08:27</t>
-  </si>
-  <si>
-    <t>2026-06-20 17:05:46</t>
-  </si>
-  <si>
-    <t>2026-06-22 08:37:39</t>
-  </si>
-  <si>
-    <t>2026-06-22 11:03:49</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:09:13</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:23:48</t>
-  </si>
-  <si>
-    <t>2026-06-23 08:25:44</t>
-  </si>
-  <si>
-    <t>2026-06-23 11:34:46</t>
-  </si>
-  <si>
-    <t>2026-06-24 07:58:51</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:29:49</t>
-  </si>
-  <si>
-    <t>2026-06-24 10:46:01</t>
-  </si>
-  <si>
-    <t>2026-06-24 12:05:19</t>
-  </si>
-  <si>
-    <t>2026-06-24 14:21:56</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>17:36:00</t>
+  </si>
+  <si>
+    <t>13:54:00</t>
+  </si>
+  <si>
+    <t>10:07:00</t>
+  </si>
+  <si>
+    <t>11:46:00</t>
+  </si>
+  <si>
+    <t>10:51:00</t>
+  </si>
+  <si>
+    <t>10:49:00</t>
+  </si>
+  <si>
+    <t>15:58:00</t>
+  </si>
+  <si>
+    <t>10:08:00</t>
+  </si>
+  <si>
+    <t>17:05:00</t>
+  </si>
+  <si>
+    <t>08:37:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>08:09:00</t>
+  </si>
+  <si>
+    <t>11:34:00</t>
+  </si>
+  <si>
+    <t>08:25:00</t>
+  </si>
+  <si>
+    <t>08:23:00</t>
+  </si>
+  <si>
+    <t>12:05:00</t>
+  </si>
+  <si>
+    <t>08:29:00</t>
+  </si>
+  <si>
+    <t>10:45:00</t>
+  </si>
+  <si>
+    <t>14:20:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>10:02:00</t>
+  </si>
+  <si>
+    <t>13:04:00</t>
+  </si>
+  <si>
+    <t>08:57:00</t>
+  </si>
+  <si>
+    <t>11:28:00</t>
+  </si>
+  <si>
+    <t>15:23:00</t>
+  </si>
+  <si>
+    <t>13:13:00</t>
+  </si>
+  <si>
+    <t>08:44:00</t>
+  </si>
+  <si>
+    <t>11:33:00</t>
+  </si>
+  <si>
+    <t>3233443640 3233443640</t>
+  </si>
+  <si>
+    <t>3233480716 3233480716</t>
+  </si>
+  <si>
+    <t>3233477954 3233477954</t>
+  </si>
+  <si>
+    <t>3233566284 3233566284</t>
+  </si>
+  <si>
+    <t>3233575615 3233575615</t>
+  </si>
+  <si>
+    <t>3233582101 3233582101</t>
+  </si>
+  <si>
+    <t>3233593252 3233593252</t>
+  </si>
+  <si>
+    <t>3233629943 3233629943</t>
+  </si>
+  <si>
+    <t>3233641882 3233641882</t>
+  </si>
+  <si>
+    <t>3233694072 3233694072</t>
+  </si>
+  <si>
+    <t>3233720507 3233720507</t>
+  </si>
+  <si>
+    <t>3233705250 3233705250</t>
+  </si>
+  <si>
+    <t>3233739682 3233739682</t>
+  </si>
+  <si>
+    <t>3233758571 3233758571</t>
+  </si>
+  <si>
+    <t>3233759407 3233759407</t>
+  </si>
+  <si>
+    <t>3233804568 3233804568</t>
+  </si>
+  <si>
+    <t>3233784465 3233784465</t>
+  </si>
+  <si>
+    <t>3233805093 3233805093</t>
+  </si>
+  <si>
+    <t>3233822356 3233822356</t>
+  </si>
+  <si>
+    <t>3233824358 3233824358</t>
+  </si>
+  <si>
+    <t>3233918969 3233918969</t>
+  </si>
+  <si>
+    <t>3233919328 3233919328</t>
+  </si>
+  <si>
+    <t>3233930790 3233930790</t>
+  </si>
+  <si>
+    <t>3234042680 3234042680</t>
+  </si>
+  <si>
+    <t>3234048811 3234048811</t>
+  </si>
+  <si>
+    <t>3234051291 3234051291</t>
+  </si>
+  <si>
+    <t>3234053969 3234053969</t>
+  </si>
+  <si>
+    <t>3234083347 3234083347</t>
+  </si>
+  <si>
+    <t>3234087767 3234087767</t>
+  </si>
+  <si>
+    <t>3234096567 3234096567</t>
   </si>
   <si>
     <t>Общи литри по продукт / СПЕДСТРОЙ ООД</t>
@@ -634,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -643,14 +787,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -684,818 +831,1447 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F2">
         <v>40.49</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2">
         <v>1.47</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>59.52</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>63.16</v>
       </c>
-      <c r="K2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="L2" t="s">
+        <v>57</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46190</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3">
         <v>1.45</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>2.9</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.55</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>3.1</v>
       </c>
-      <c r="K3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46191</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F4">
         <v>300.01</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4">
         <v>1.53</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>459.02</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.58</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>474.02</v>
       </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46192</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F5">
+        <v>40.14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5">
+        <v>1.53</v>
+      </c>
+      <c r="I5" s="1">
+        <v>61.41</v>
+      </c>
+      <c r="J5">
+        <v>1.56</v>
+      </c>
+      <c r="K5" s="1">
+        <v>62.62</v>
+      </c>
+      <c r="L5" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H5">
-        <v>91.8</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J5">
-        <v>93.59999999999999</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>113200</v>
+      </c>
+      <c r="N5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46192</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F6">
         <v>32.47</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6">
         <v>1.45</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>47.08</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>50</v>
       </c>
-      <c r="K6" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46192</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F7">
-        <v>40.14</v>
-      </c>
-      <c r="G7" s="1">
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7">
         <v>1.53</v>
       </c>
-      <c r="H7">
-        <v>61.41</v>
-      </c>
       <c r="I7" s="1">
+        <v>91.8</v>
+      </c>
+      <c r="J7">
         <v>1.56</v>
       </c>
-      <c r="J7">
-        <v>62.62</v>
-      </c>
-      <c r="K7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="K7" s="1">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="L7" t="s">
+        <v>62</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46192</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F8">
         <v>49.19</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8">
         <v>1.79</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>88.05</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.82</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>89.53</v>
       </c>
-      <c r="K8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46193</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F9">
         <v>300</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9">
         <v>1.49</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>447</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.54</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>462</v>
       </c>
-      <c r="K9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>64</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46193</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F10">
         <v>67.33</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10">
         <v>1.49</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>100.32</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.54</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>103.69</v>
       </c>
-      <c r="K10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>65</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46195</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D11" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F11">
         <v>150</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11">
         <v>1.46</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>219</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.52</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>228</v>
       </c>
-      <c r="K11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46195</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F12">
         <v>70.75</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12">
         <v>1.46</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>103.3</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.52</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>107.54</v>
       </c>
-      <c r="K12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12">
+        <v>242890</v>
+      </c>
+      <c r="N12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46196</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F13">
         <v>300</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13">
         <v>1.46</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="1">
         <v>438</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13">
         <v>1.52</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="1">
         <v>456</v>
       </c>
-      <c r="K13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="L13" t="s">
+        <v>68</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46196</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E14" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F14">
-        <v>150</v>
-      </c>
-      <c r="G14" s="1">
+        <v>77.23999999999999</v>
+      </c>
+      <c r="G14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14">
         <v>1.46</v>
       </c>
-      <c r="H14">
-        <v>219</v>
-      </c>
       <c r="I14" s="1">
+        <v>112.77</v>
+      </c>
+      <c r="J14">
         <v>1.52</v>
       </c>
-      <c r="J14">
-        <v>228</v>
-      </c>
-      <c r="K14" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="K14" s="1">
+        <v>117.4</v>
+      </c>
+      <c r="L14" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46196</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E15" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F15">
         <v>150</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15">
         <v>1.46</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="1">
         <v>219</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>1.52</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>228</v>
       </c>
-      <c r="K15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>70</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46196</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E16" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F16">
-        <v>77.23999999999999</v>
-      </c>
-      <c r="G16" s="1">
+        <v>150</v>
+      </c>
+      <c r="G16" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16">
         <v>1.46</v>
       </c>
-      <c r="H16">
-        <v>112.77</v>
-      </c>
       <c r="I16" s="1">
+        <v>219</v>
+      </c>
+      <c r="J16">
         <v>1.52</v>
       </c>
-      <c r="J16">
-        <v>117.4</v>
-      </c>
-      <c r="K16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="K16" s="1">
+        <v>228</v>
+      </c>
+      <c r="L16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46197</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="F17">
-        <v>37.73</v>
-      </c>
-      <c r="G17" s="1">
-        <v>1.4</v>
+        <v>60.01</v>
+      </c>
+      <c r="G17" t="s">
+        <v>56</v>
       </c>
       <c r="H17">
-        <v>52.82</v>
+        <v>1.45</v>
       </c>
       <c r="I17" s="1">
+        <v>87.01000000000001</v>
+      </c>
+      <c r="J17">
         <v>1.51</v>
       </c>
-      <c r="J17">
-        <v>56.97</v>
-      </c>
-      <c r="K17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="K17" s="1">
+        <v>90.62</v>
+      </c>
+      <c r="L17" t="s">
+        <v>72</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46197</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F18">
         <v>64.31</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18">
         <v>1.45</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>93.25</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.52</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>97.75</v>
       </c>
-      <c r="K18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>73</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46197</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F19">
         <v>59.05</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>56</v>
+      </c>
+      <c r="H19">
         <v>1.45</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>85.62</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.51</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>89.17</v>
       </c>
-      <c r="K19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46197</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="F20">
-        <v>60.01</v>
-      </c>
-      <c r="G20" s="1">
+        <v>70</v>
+      </c>
+      <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20">
         <v>1.45</v>
       </c>
-      <c r="H20">
-        <v>87.01000000000001</v>
-      </c>
       <c r="I20" s="1">
+        <v>101.5</v>
+      </c>
+      <c r="J20">
         <v>1.51</v>
       </c>
-      <c r="J20">
-        <v>90.62</v>
-      </c>
-      <c r="K20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="K20" s="1">
+        <v>105.7</v>
+      </c>
+      <c r="L20" t="s">
+        <v>75</v>
+      </c>
+      <c r="M20">
+        <v>231863</v>
+      </c>
+      <c r="N20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46197</v>
       </c>
       <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>37</v>
+      </c>
+      <c r="E21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21">
+        <v>37.73</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21">
+        <v>1.4</v>
+      </c>
+      <c r="I21" s="1">
+        <v>52.82</v>
+      </c>
+      <c r="J21">
+        <v>1.51</v>
+      </c>
+      <c r="K21" s="1">
+        <v>56.97</v>
+      </c>
+      <c r="L21" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" t="s">
+        <v>54</v>
+      </c>
+      <c r="F22">
+        <v>300.01</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22">
+        <v>1.43</v>
+      </c>
+      <c r="I22" s="1">
+        <v>429.01</v>
+      </c>
+      <c r="J22">
+        <v>1.51</v>
+      </c>
+      <c r="K22" s="1">
+        <v>453.02</v>
+      </c>
+      <c r="L22" t="s">
+        <v>62</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
+        <v>56</v>
+      </c>
+      <c r="H23">
+        <v>1.43</v>
+      </c>
+      <c r="I23" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="J23">
+        <v>1.51</v>
+      </c>
+      <c r="K23" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B24" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C24" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24">
+        <v>42.91</v>
+      </c>
+      <c r="G24" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24">
+        <v>1.43</v>
+      </c>
+      <c r="I24" s="1">
+        <v>61.36</v>
+      </c>
+      <c r="J24">
+        <v>1.51</v>
+      </c>
+      <c r="K24" s="1">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="L24" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F25">
+        <v>250</v>
+      </c>
+      <c r="G25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25">
+        <v>1.42</v>
+      </c>
+      <c r="I25" s="1">
+        <v>355</v>
+      </c>
+      <c r="J25">
+        <v>1.51</v>
+      </c>
+      <c r="K25" s="1">
+        <v>377.5</v>
+      </c>
+      <c r="L25" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+      <c r="E26" t="s">
+        <v>54</v>
+      </c>
+      <c r="F26">
+        <v>280.02</v>
+      </c>
+      <c r="G26" t="s">
+        <v>56</v>
+      </c>
+      <c r="H26">
+        <v>1.42</v>
+      </c>
+      <c r="I26" s="1">
+        <v>397.63</v>
+      </c>
+      <c r="J26">
+        <v>1.51</v>
+      </c>
+      <c r="K26" s="1">
+        <v>422.83</v>
+      </c>
+      <c r="L26" t="s">
+        <v>80</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B27" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27">
         <v>30</v>
       </c>
-      <c r="D21" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21">
-        <v>70</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.45</v>
-      </c>
-      <c r="H21">
-        <v>101.5</v>
-      </c>
-      <c r="I21" s="1">
+      <c r="G27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27">
+        <v>1.42</v>
+      </c>
+      <c r="I27" s="1">
+        <v>42.6</v>
+      </c>
+      <c r="J27">
         <v>1.51</v>
       </c>
-      <c r="J21">
-        <v>105.7</v>
-      </c>
-      <c r="K21" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26" s="7">
-        <v>1918.84</v>
-      </c>
-      <c r="C26" s="7">
+      <c r="K27" s="1">
+        <v>45.3</v>
+      </c>
+      <c r="L27" t="s">
+        <v>58</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B28" t="s">
         <v>15</v>
       </c>
-      <c r="D26" s="8">
-        <v>1.479</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2838</v>
-      </c>
-      <c r="F26" s="7">
-        <v>2944.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="B27" s="7">
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28">
+        <v>183.46</v>
+      </c>
+      <c r="G28" t="s">
+        <v>56</v>
+      </c>
+      <c r="H28">
+        <v>1.42</v>
+      </c>
+      <c r="I28" s="1">
+        <v>260.51</v>
+      </c>
+      <c r="J28">
+        <v>1.51</v>
+      </c>
+      <c r="K28" s="1">
+        <v>277.02</v>
+      </c>
+      <c r="L28" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28">
+        <v>99148</v>
+      </c>
+      <c r="N28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29">
+        <v>44.03</v>
+      </c>
+      <c r="G29" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29">
+        <v>1.42</v>
+      </c>
+      <c r="I29" s="1">
+        <v>62.52</v>
+      </c>
+      <c r="J29">
+        <v>1.51</v>
+      </c>
+      <c r="K29" s="1">
+        <v>66.48999999999999</v>
+      </c>
+      <c r="L29" t="s">
+        <v>82</v>
+      </c>
+      <c r="M29">
+        <v>113900</v>
+      </c>
+      <c r="N29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="G30" t="s">
+        <v>56</v>
+      </c>
+      <c r="H30">
+        <v>1.42</v>
+      </c>
+      <c r="I30" s="1">
+        <v>142</v>
+      </c>
+      <c r="J30">
+        <v>1.51</v>
+      </c>
+      <c r="K30" s="1">
+        <v>151</v>
+      </c>
+      <c r="L30" t="s">
+        <v>83</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="3">
+        <v>46203</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31">
+        <v>165</v>
+      </c>
+      <c r="G31" t="s">
+        <v>56</v>
+      </c>
+      <c r="H31">
+        <v>1.42</v>
+      </c>
+      <c r="I31" s="1">
+        <v>234.3</v>
+      </c>
+      <c r="J31">
+        <v>1.51</v>
+      </c>
+      <c r="K31" s="1">
+        <v>249.15</v>
+      </c>
+      <c r="L31" t="s">
+        <v>84</v>
+      </c>
+      <c r="M31">
+        <v>193230</v>
+      </c>
+      <c r="N31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="7">
+        <v>3344.27</v>
+      </c>
+      <c r="C36" s="7">
+        <v>25</v>
+      </c>
+      <c r="D36" s="8">
+        <v>1.455</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4865.83</v>
+      </c>
+      <c r="F36" s="7">
+        <v>5096.51</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="7">
         <v>112.69</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C37" s="7">
         <v>4</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D37" s="8">
         <v>1.4404</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E37" s="7">
         <v>162.32</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F37" s="7">
         <v>173.23</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="7">
+    <row r="38" spans="1:6">
+      <c r="A38" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="7">
         <v>49.19</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C38" s="7">
         <v>1</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D38" s="8">
         <v>1.79</v>
       </c>
-      <c r="E28" s="7">
+      <c r="E38" s="7">
         <v>88.05</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F38" s="7">
         <v>89.53</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="10">
-        <v>2080.72</v>
-      </c>
-      <c r="C29" s="10">
-        <v>20</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="10">
-        <v>3088.37</v>
-      </c>
-      <c r="F29" s="10">
-        <v>3206.87</v>
+    <row r="39" spans="1:6">
+      <c r="A39" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="B39" s="10">
+        <v>3506.15</v>
+      </c>
+      <c r="C39" s="10">
+        <v>30</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="10">
+        <v>5116.2</v>
+      </c>
+      <c r="F39" s="10">
+        <v>5359.27</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
@@ -503,7 +503,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -2891,7 +2891,7 @@
         <v>36</v>
       </c>
       <c r="D49" s="8">
-        <v>1.5873</v>
+        <v>1.587334</v>
       </c>
       <c r="E49" s="7">
         <v>6169.27</v>
@@ -2911,7 +2911,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="8">
-        <v>1.4455</v>
+        <v>1.445525</v>
       </c>
       <c r="E50" s="7">
         <v>433.86</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="161">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -895,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -908,13 +911,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -957,1902 +960,2034 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2">
-        <v>42.39</v>
+        <v>42.391</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H2">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I2" s="1">
-        <v>64.43000000000001</v>
+        <v>1.519</v>
       </c>
       <c r="J2">
+        <v>64.391929</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.61</v>
       </c>
-      <c r="K2" s="1">
-        <v>68.25</v>
-      </c>
-      <c r="L2" t="s">
-        <v>69</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="L2" s="1">
+        <v>68.24951</v>
+      </c>
+      <c r="M2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F3">
         <v>300</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H3">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I3" s="1">
-        <v>456</v>
+        <v>1.519</v>
       </c>
       <c r="J3">
+        <v>455.7</v>
+      </c>
+      <c r="K3" s="1">
         <v>1.61</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>483</v>
       </c>
-      <c r="L3" t="s">
-        <v>70</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="M3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F4">
-        <v>210.01</v>
+        <v>210.012</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H4">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I4" s="1">
-        <v>319.22</v>
+        <v>1.519</v>
       </c>
       <c r="J4">
+        <v>319.008228</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.61</v>
       </c>
-      <c r="K4" s="1">
-        <v>338.12</v>
-      </c>
-      <c r="L4" t="s">
-        <v>71</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="1">
+        <v>338.11932</v>
+      </c>
+      <c r="M4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N4">
         <v>232402</v>
       </c>
-      <c r="N4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F5">
-        <v>43.52</v>
+        <v>43.521</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I5" s="1">
-        <v>66.15000000000001</v>
+        <v>1.519</v>
       </c>
       <c r="J5">
+        <v>66.10839900000001</v>
+      </c>
+      <c r="K5" s="1">
         <v>1.63</v>
       </c>
-      <c r="K5" s="1">
-        <v>70.94</v>
-      </c>
-      <c r="L5" t="s">
-        <v>72</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="L5" s="1">
+        <v>70.93922999999999</v>
+      </c>
+      <c r="M5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F6">
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H6">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I6" s="1">
-        <v>53.2</v>
+        <v>1.519</v>
       </c>
       <c r="J6">
+        <v>53.165</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.63</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>57.05</v>
       </c>
-      <c r="L6" t="s">
-        <v>73</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="M6" t="s">
+        <v>74</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F7">
         <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I7" s="1">
-        <v>364.8</v>
+        <v>1.519</v>
       </c>
       <c r="J7">
+        <v>364.56</v>
+      </c>
+      <c r="K7" s="1">
         <v>1.63</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>391.2</v>
       </c>
-      <c r="L7" t="s">
-        <v>74</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="M7" t="s">
+        <v>75</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3">
         <v>46220</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F8">
         <v>62.46</v>
       </c>
       <c r="G8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H8">
-        <v>1.52</v>
+        <v>1.499</v>
       </c>
       <c r="I8" s="1">
-        <v>94.94</v>
+        <v>1.519</v>
       </c>
       <c r="J8">
+        <v>94.87674</v>
+      </c>
+      <c r="K8" s="1">
         <v>1.63</v>
       </c>
-      <c r="K8" s="1">
-        <v>101.81</v>
-      </c>
-      <c r="L8" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="L8" s="1">
+        <v>101.8098</v>
+      </c>
+      <c r="M8" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3">
         <v>46221</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9">
-        <v>27.1</v>
+        <v>27.103</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9">
-        <v>1.55</v>
+        <v>1.528</v>
       </c>
       <c r="I9" s="1">
-        <v>42</v>
+        <v>1.548</v>
       </c>
       <c r="J9">
+        <v>41.955444</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.65</v>
       </c>
-      <c r="K9" s="1">
-        <v>44.72</v>
-      </c>
-      <c r="L9" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9">
+      <c r="L9" s="1">
+        <v>44.71995</v>
+      </c>
+      <c r="M9" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9">
         <v>232558</v>
       </c>
-      <c r="N9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3">
         <v>46222</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H10">
-        <v>1.55</v>
+        <v>1.528</v>
       </c>
       <c r="I10" s="1">
-        <v>31</v>
+        <v>1.548</v>
       </c>
       <c r="J10">
+        <v>30.96</v>
+      </c>
+      <c r="K10" s="1">
         <v>1.68</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>33.6</v>
       </c>
-      <c r="L10" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="M10" t="s">
+        <v>78</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3">
         <v>46223</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F11">
-        <v>46.95</v>
+        <v>46.952</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H11">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I11" s="1">
-        <v>73.70999999999999</v>
+        <v>1.566</v>
       </c>
       <c r="J11">
+        <v>73.526832</v>
+      </c>
+      <c r="K11" s="1">
         <v>1.67</v>
       </c>
-      <c r="K11" s="1">
-        <v>78.41</v>
-      </c>
-      <c r="L11" t="s">
-        <v>78</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="L11" s="1">
+        <v>78.40984</v>
+      </c>
+      <c r="M11" t="s">
+        <v>79</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3">
         <v>46223</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F12">
-        <v>79.48</v>
+        <v>79.482</v>
       </c>
       <c r="G12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H12">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I12" s="1">
-        <v>124.78</v>
+        <v>1.566</v>
       </c>
       <c r="J12">
+        <v>124.468812</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.68</v>
       </c>
-      <c r="K12" s="1">
-        <v>133.53</v>
-      </c>
-      <c r="L12" t="s">
-        <v>74</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="L12" s="1">
+        <v>133.52976</v>
+      </c>
+      <c r="M12" t="s">
+        <v>75</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3">
         <v>46223</v>
       </c>
       <c r="B13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13">
-        <v>150.01</v>
+        <v>150.012</v>
       </c>
       <c r="G13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H13">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I13" s="1">
-        <v>235.52</v>
+        <v>1.566</v>
       </c>
       <c r="J13">
+        <v>234.918792</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.68</v>
       </c>
-      <c r="K13" s="1">
-        <v>252.02</v>
-      </c>
-      <c r="L13" t="s">
-        <v>79</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="L13" s="1">
+        <v>252.02016</v>
+      </c>
+      <c r="M13" t="s">
+        <v>80</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3">
         <v>46223</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14">
         <v>150</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H14">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I14" s="1">
-        <v>235.5</v>
+        <v>1.566</v>
       </c>
       <c r="J14">
+        <v>234.9</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.68</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>252</v>
       </c>
-      <c r="L14" t="s">
-        <v>80</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="M14" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3">
         <v>46223</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F15">
-        <v>226.51</v>
+        <v>226.512</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H15">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I15" s="1">
-        <v>355.62</v>
+        <v>1.566</v>
       </c>
       <c r="J15">
+        <v>354.717792</v>
+      </c>
+      <c r="K15" s="1">
         <v>1.68</v>
       </c>
-      <c r="K15" s="1">
-        <v>380.54</v>
-      </c>
-      <c r="L15" t="s">
-        <v>81</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="1">
+        <v>380.54016</v>
+      </c>
+      <c r="M15" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15">
         <v>176492</v>
       </c>
-      <c r="N15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="O15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3">
         <v>46223</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16">
         <v>213.03</v>
       </c>
       <c r="G16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H16">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I16" s="1">
-        <v>334.46</v>
+        <v>1.566</v>
       </c>
       <c r="J16">
+        <v>333.60498</v>
+      </c>
+      <c r="K16" s="1">
         <v>1.68</v>
       </c>
-      <c r="K16" s="1">
-        <v>357.89</v>
-      </c>
-      <c r="L16" t="s">
-        <v>82</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>357.8904</v>
+      </c>
+      <c r="M16" t="s">
+        <v>83</v>
+      </c>
+      <c r="N16">
         <v>100133</v>
       </c>
-      <c r="N16" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="3">
         <v>46223</v>
       </c>
       <c r="B17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17">
-        <v>35.71</v>
+        <v>35.708</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17">
-        <v>1.57</v>
+        <v>1.546</v>
       </c>
       <c r="I17" s="1">
-        <v>56.06</v>
+        <v>1.566</v>
       </c>
       <c r="J17">
+        <v>55.918728</v>
+      </c>
+      <c r="K17" s="1">
         <v>1.68</v>
       </c>
-      <c r="K17" s="1">
-        <v>59.99</v>
-      </c>
-      <c r="L17" t="s">
-        <v>83</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="L17" s="1">
+        <v>59.98944</v>
+      </c>
+      <c r="M17" t="s">
+        <v>84</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="3">
         <v>46223</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18">
-        <v>36.45</v>
+        <v>36.451</v>
       </c>
       <c r="G18" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H18">
-        <v>1.42</v>
+        <v>1.389</v>
       </c>
       <c r="I18" s="1">
-        <v>51.76</v>
+        <v>1.419</v>
       </c>
       <c r="J18">
+        <v>51.723969</v>
+      </c>
+      <c r="K18" s="1">
         <v>1.53</v>
       </c>
-      <c r="K18" s="1">
-        <v>55.77</v>
-      </c>
-      <c r="L18" t="s">
-        <v>84</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="1">
+        <v>55.77003</v>
+      </c>
+      <c r="M18" t="s">
+        <v>85</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3">
         <v>46224</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>235</v>
       </c>
       <c r="G19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H19">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I19" s="1">
-        <v>371.3</v>
+        <v>1.584</v>
       </c>
       <c r="J19">
+        <v>372.24</v>
+      </c>
+      <c r="K19" s="1">
         <v>1.68</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>394.8</v>
       </c>
-      <c r="L19" t="s">
-        <v>85</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="M19" t="s">
+        <v>86</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3">
         <v>46224</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F20">
-        <v>83.34999999999999</v>
+        <v>83.351</v>
       </c>
       <c r="G20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H20">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I20" s="1">
-        <v>131.69</v>
+        <v>1.584</v>
       </c>
       <c r="J20">
+        <v>132.027984</v>
+      </c>
+      <c r="K20" s="1">
         <v>1.68</v>
       </c>
-      <c r="K20" s="1">
-        <v>140.03</v>
-      </c>
-      <c r="L20" t="s">
-        <v>86</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="1">
+        <v>140.02968</v>
+      </c>
+      <c r="M20" t="s">
+        <v>87</v>
+      </c>
+      <c r="N20">
         <v>233368</v>
       </c>
-      <c r="N20" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3">
         <v>46224</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F21">
-        <v>150.01</v>
+        <v>150.012</v>
       </c>
       <c r="G21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H21">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I21" s="1">
-        <v>237.02</v>
+        <v>1.584</v>
       </c>
       <c r="J21">
+        <v>237.619008</v>
+      </c>
+      <c r="K21" s="1">
         <v>1.68</v>
       </c>
-      <c r="K21" s="1">
-        <v>252.02</v>
-      </c>
-      <c r="L21" t="s">
-        <v>87</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="L21" s="1">
+        <v>252.02016</v>
+      </c>
+      <c r="M21" t="s">
+        <v>88</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="3">
         <v>46224</v>
       </c>
       <c r="B22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F22">
-        <v>34.2</v>
+        <v>34.202</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H22">
-        <v>1.58</v>
+        <v>1.564</v>
       </c>
       <c r="I22" s="1">
-        <v>54.04</v>
+        <v>1.584</v>
       </c>
       <c r="J22">
+        <v>54.175968</v>
+      </c>
+      <c r="K22" s="1">
         <v>1.68</v>
       </c>
-      <c r="K22" s="1">
-        <v>57.46</v>
-      </c>
-      <c r="L22" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="1">
+        <v>57.45936</v>
+      </c>
+      <c r="M22" t="s">
+        <v>89</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3">
         <v>46225</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F23">
-        <v>300.02</v>
+        <v>300.018</v>
       </c>
       <c r="G23" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H23">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I23" s="1">
-        <v>483.03</v>
+        <v>1.608</v>
       </c>
       <c r="J23">
+        <v>482.428944</v>
+      </c>
+      <c r="K23" s="1">
         <v>1.69</v>
       </c>
-      <c r="K23" s="1">
-        <v>507.03</v>
-      </c>
-      <c r="L23" t="s">
-        <v>89</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-      <c r="N23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="L23" s="1">
+        <v>507.03042</v>
+      </c>
+      <c r="M23" t="s">
+        <v>90</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="3">
         <v>46225</v>
       </c>
       <c r="B24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F24">
-        <v>64.7</v>
+        <v>64.69799999999999</v>
       </c>
       <c r="G24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H24">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I24" s="1">
-        <v>104.17</v>
+        <v>1.608</v>
       </c>
       <c r="J24">
+        <v>104.034384</v>
+      </c>
+      <c r="K24" s="1">
         <v>1.69</v>
       </c>
-      <c r="K24" s="1">
-        <v>109.34</v>
-      </c>
-      <c r="L24" t="s">
-        <v>90</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="1">
+        <v>109.33962</v>
+      </c>
+      <c r="M24" t="s">
+        <v>91</v>
+      </c>
+      <c r="N24">
         <v>243441</v>
       </c>
-      <c r="N24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3">
         <v>46225</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F25">
         <v>250</v>
       </c>
       <c r="G25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H25">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I25" s="1">
-        <v>402.5</v>
+        <v>1.608</v>
       </c>
       <c r="J25">
+        <v>402</v>
+      </c>
+      <c r="K25" s="1">
         <v>1.69</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>422.5</v>
       </c>
-      <c r="L25" t="s">
-        <v>91</v>
-      </c>
-      <c r="M25">
+      <c r="M25" t="s">
+        <v>92</v>
+      </c>
+      <c r="N25">
         <v>194160</v>
       </c>
-      <c r="N25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="O25" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="3">
         <v>46226</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E26" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F26">
-        <v>58.16</v>
+        <v>58.159</v>
       </c>
       <c r="G26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H26">
-        <v>1.61</v>
+        <v>1.588</v>
       </c>
       <c r="I26" s="1">
-        <v>93.64</v>
+        <v>1.608</v>
       </c>
       <c r="J26">
+        <v>93.519672</v>
+      </c>
+      <c r="K26" s="1">
         <v>1.7</v>
       </c>
-      <c r="K26" s="1">
-        <v>98.87</v>
-      </c>
-      <c r="L26" t="s">
-        <v>92</v>
-      </c>
-      <c r="M26">
-        <v>0</v>
-      </c>
-      <c r="N26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="L26" s="1">
+        <v>98.8703</v>
+      </c>
+      <c r="M26" t="s">
+        <v>93</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="3">
         <v>46226</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F27">
-        <v>47.33</v>
+        <v>47.331</v>
       </c>
       <c r="G27" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H27">
-        <v>1.43</v>
+        <v>1.401</v>
       </c>
       <c r="I27" s="1">
-        <v>67.68000000000001</v>
+        <v>1.431</v>
       </c>
       <c r="J27">
+        <v>67.730661</v>
+      </c>
+      <c r="K27" s="1">
         <v>1.54</v>
       </c>
-      <c r="K27" s="1">
-        <v>72.89</v>
-      </c>
-      <c r="L27" t="s">
-        <v>93</v>
-      </c>
-      <c r="M27">
-        <v>0</v>
-      </c>
-      <c r="N27" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="L27" s="1">
+        <v>72.88974</v>
+      </c>
+      <c r="M27" t="s">
+        <v>94</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="3">
         <v>46226</v>
       </c>
       <c r="B28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F28">
         <v>42.5</v>
       </c>
       <c r="G28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H28">
-        <v>1.43</v>
+        <v>1.401</v>
       </c>
       <c r="I28" s="1">
-        <v>60.78</v>
+        <v>1.431</v>
       </c>
       <c r="J28">
+        <v>60.8175</v>
+      </c>
+      <c r="K28" s="1">
         <v>1.54</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>65.45</v>
       </c>
-      <c r="L28" t="s">
-        <v>94</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
-      <c r="N28" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="M28" t="s">
+        <v>95</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F29">
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H29">
-        <v>1.43</v>
+        <v>1.401</v>
       </c>
       <c r="I29" s="1">
-        <v>28.6</v>
+        <v>1.431</v>
       </c>
       <c r="J29">
+        <v>28.62</v>
+      </c>
+      <c r="K29" s="1">
         <v>1.54</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>30.8</v>
       </c>
-      <c r="L29" t="s">
-        <v>95</v>
-      </c>
-      <c r="M29">
-        <v>0</v>
-      </c>
-      <c r="N29" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="M29" t="s">
+        <v>96</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="3">
         <v>46227</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F30">
         <v>45</v>
       </c>
       <c r="G30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H30">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I30" s="1">
-        <v>73.8</v>
+        <v>1.639</v>
       </c>
       <c r="J30">
+        <v>73.755</v>
+      </c>
+      <c r="K30" s="1">
         <v>1.72</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>77.40000000000001</v>
       </c>
-      <c r="L30" t="s">
-        <v>96</v>
-      </c>
-      <c r="M30">
-        <v>0</v>
-      </c>
-      <c r="N30" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="M30" t="s">
+        <v>97</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="3">
         <v>46227</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F31">
-        <v>54.03</v>
+        <v>54.029</v>
       </c>
       <c r="G31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H31">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I31" s="1">
-        <v>88.61</v>
+        <v>1.639</v>
       </c>
       <c r="J31">
+        <v>88.55353100000001</v>
+      </c>
+      <c r="K31" s="1">
         <v>1.7</v>
       </c>
-      <c r="K31" s="1">
-        <v>91.84999999999999</v>
-      </c>
-      <c r="L31" t="s">
-        <v>97</v>
-      </c>
-      <c r="M31">
-        <v>0</v>
-      </c>
-      <c r="N31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="L31" s="1">
+        <v>91.8493</v>
+      </c>
+      <c r="M31" t="s">
+        <v>98</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="3">
         <v>46227</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F32">
         <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H32">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I32" s="1">
-        <v>109.88</v>
+        <v>1.639</v>
       </c>
       <c r="J32">
+        <v>109.813</v>
+      </c>
+      <c r="K32" s="1">
         <v>1.72</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>115.24</v>
       </c>
-      <c r="L32" t="s">
-        <v>98</v>
-      </c>
-      <c r="M32">
+      <c r="M32" t="s">
+        <v>99</v>
+      </c>
+      <c r="N32">
         <v>500995</v>
       </c>
-      <c r="N32" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+      <c r="O32" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" s="3">
         <v>46228</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F33">
         <v>47.82</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H33">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I33" s="1">
-        <v>78.42</v>
+        <v>1.639</v>
       </c>
       <c r="J33">
+        <v>78.37698</v>
+      </c>
+      <c r="K33" s="1">
         <v>1.72</v>
       </c>
-      <c r="K33" s="1">
-        <v>82.25</v>
-      </c>
-      <c r="L33" t="s">
-        <v>99</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+      <c r="L33" s="1">
+        <v>82.2504</v>
+      </c>
+      <c r="M33" t="s">
+        <v>100</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" s="3">
         <v>46228</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F34">
-        <v>35.48</v>
+        <v>35.483</v>
       </c>
       <c r="G34" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H34">
-        <v>1.64</v>
+        <v>1.619</v>
       </c>
       <c r="I34" s="1">
-        <v>58.19</v>
+        <v>1.639</v>
       </c>
       <c r="J34">
+        <v>58.156637</v>
+      </c>
+      <c r="K34" s="1">
         <v>1.74</v>
       </c>
-      <c r="K34" s="1">
-        <v>61.74</v>
-      </c>
-      <c r="L34" t="s">
-        <v>100</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+      <c r="L34" s="1">
+        <v>61.74042</v>
+      </c>
+      <c r="M34" t="s">
+        <v>101</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" s="3">
         <v>46229</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D35" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F35">
         <v>45</v>
       </c>
       <c r="G35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H35">
-        <v>1.43</v>
+        <v>1.401</v>
       </c>
       <c r="I35" s="1">
-        <v>64.34999999999999</v>
+        <v>1.431</v>
       </c>
       <c r="J35">
+        <v>64.395</v>
+      </c>
+      <c r="K35" s="1">
         <v>1.56</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>70.2</v>
       </c>
-      <c r="L35" t="s">
-        <v>101</v>
-      </c>
-      <c r="M35">
-        <v>0</v>
-      </c>
-      <c r="N35" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+      <c r="M35" t="s">
+        <v>102</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" s="3">
         <v>46231</v>
       </c>
       <c r="B36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H36">
-        <v>1.67</v>
+        <v>1.653</v>
       </c>
       <c r="I36" s="1">
-        <v>167</v>
+        <v>1.673</v>
       </c>
       <c r="J36">
+        <v>167.3</v>
+      </c>
+      <c r="K36" s="1">
         <v>1.75</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>175</v>
       </c>
-      <c r="L36" t="s">
-        <v>102</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+      <c r="M36" t="s">
+        <v>103</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" s="3">
         <v>46231</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F37">
         <v>207.72</v>
       </c>
       <c r="G37" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H37">
-        <v>1.67</v>
+        <v>1.653</v>
       </c>
       <c r="I37" s="1">
-        <v>346.89</v>
+        <v>1.673</v>
       </c>
       <c r="J37">
+        <v>347.51556</v>
+      </c>
+      <c r="K37" s="1">
         <v>1.75</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>363.51</v>
       </c>
-      <c r="L37" t="s">
-        <v>103</v>
-      </c>
-      <c r="M37">
+      <c r="M37" t="s">
+        <v>104</v>
+      </c>
+      <c r="N37">
         <v>100517</v>
       </c>
-      <c r="N37" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+      <c r="O37" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" s="3">
         <v>46231</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E38" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F38">
-        <v>42.64</v>
+        <v>42.641</v>
       </c>
       <c r="G38" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H38">
-        <v>1.47</v>
+        <v>1.441</v>
       </c>
       <c r="I38" s="1">
-        <v>62.68</v>
+        <v>1.471</v>
       </c>
       <c r="J38">
+        <v>62.724911</v>
+      </c>
+      <c r="K38" s="1">
         <v>1.56</v>
       </c>
-      <c r="K38" s="1">
-        <v>66.52</v>
-      </c>
-      <c r="L38" t="s">
-        <v>104</v>
-      </c>
-      <c r="M38">
-        <v>0</v>
-      </c>
-      <c r="N38" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+      <c r="L38" s="1">
+        <v>66.51996</v>
+      </c>
+      <c r="M38" t="s">
+        <v>105</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" s="3">
         <v>46232</v>
       </c>
       <c r="B39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F39">
         <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H39">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I39" s="1">
-        <v>76.05</v>
+        <v>1.694</v>
       </c>
       <c r="J39">
+        <v>76.23</v>
+      </c>
+      <c r="K39" s="1">
         <v>1.75</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>78.75</v>
       </c>
-      <c r="L39" t="s">
-        <v>105</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+      <c r="M39" t="s">
+        <v>106</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" s="3">
         <v>46232</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40">
         <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H40">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I40" s="1">
-        <v>101.4</v>
+        <v>1.694</v>
       </c>
       <c r="J40">
+        <v>101.64</v>
+      </c>
+      <c r="K40" s="1">
         <v>1.75</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>105</v>
       </c>
-      <c r="L40" t="s">
-        <v>106</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+      <c r="M40" t="s">
+        <v>107</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" s="3">
         <v>46232</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41">
-        <v>66.22</v>
+        <v>66.21899999999999</v>
       </c>
       <c r="G41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H41">
-        <v>1.48</v>
+        <v>1.449</v>
       </c>
       <c r="I41" s="1">
-        <v>98.01000000000001</v>
+        <v>1.479</v>
       </c>
       <c r="J41">
+        <v>97.937901</v>
+      </c>
+      <c r="K41" s="1">
         <v>1.55</v>
       </c>
-      <c r="K41" s="1">
-        <v>102.64</v>
-      </c>
-      <c r="L41" t="s">
-        <v>107</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+      <c r="L41" s="1">
+        <v>102.63945</v>
+      </c>
+      <c r="M41" t="s">
+        <v>108</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F42">
-        <v>57.4</v>
+        <v>57.398</v>
       </c>
       <c r="G42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H42">
-        <v>1.69</v>
+        <v>1.674</v>
       </c>
       <c r="I42" s="1">
-        <v>97.01000000000001</v>
+        <v>1.694</v>
       </c>
       <c r="J42">
+        <v>97.232212</v>
+      </c>
+      <c r="K42" s="1">
         <v>1.76</v>
       </c>
-      <c r="K42" s="1">
-        <v>101.02</v>
-      </c>
-      <c r="L42" t="s">
-        <v>108</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+      <c r="L42" s="1">
+        <v>101.02048</v>
+      </c>
+      <c r="M42" t="s">
+        <v>109</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" s="3">
         <v>46234</v>
       </c>
       <c r="B43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F43">
-        <v>39.23</v>
+        <v>39.232</v>
       </c>
       <c r="G43" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H43">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I43" s="1">
-        <v>67.08</v>
+        <v>1.709</v>
       </c>
       <c r="J43">
+        <v>67.047488</v>
+      </c>
+      <c r="K43" s="1">
         <v>1.77</v>
       </c>
-      <c r="K43" s="1">
-        <v>69.44</v>
-      </c>
-      <c r="L43" t="s">
-        <v>109</v>
-      </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
-      <c r="N43" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+      <c r="L43" s="1">
+        <v>69.44064</v>
+      </c>
+      <c r="M43" t="s">
+        <v>110</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" s="3">
         <v>46234</v>
       </c>
       <c r="B44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F44">
-        <v>70.27</v>
+        <v>70.27200000000001</v>
       </c>
       <c r="G44" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H44">
-        <v>1.71</v>
+        <v>1.689</v>
       </c>
       <c r="I44" s="1">
-        <v>120.16</v>
+        <v>1.709</v>
       </c>
       <c r="J44">
+        <v>120.094848</v>
+      </c>
+      <c r="K44" s="1">
         <v>1.8</v>
       </c>
-      <c r="K44" s="1">
-        <v>126.49</v>
-      </c>
-      <c r="L44" t="s">
-        <v>110</v>
-      </c>
-      <c r="M44">
-        <v>0</v>
-      </c>
-      <c r="N44" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="L44" s="1">
+        <v>126.4896</v>
+      </c>
+      <c r="M44" t="s">
+        <v>111</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2860,41 +2995,41 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:15">
       <c r="A48" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B49" s="7">
-        <v>3886.56</v>
+        <v>3886.577</v>
       </c>
       <c r="C49" s="7">
         <v>36</v>
       </c>
       <c r="D49" s="8">
-        <v>1.587334</v>
+        <v>1.586626</v>
       </c>
       <c r="E49" s="7">
-        <v>6169.27</v>
+        <v>6166.54</v>
       </c>
       <c r="F49" s="7">
         <v>6532.81</v>
@@ -2902,19 +3037,19 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B50" s="7">
-        <v>300.14</v>
+        <v>300.142</v>
       </c>
       <c r="C50" s="7">
         <v>7</v>
       </c>
       <c r="D50" s="8">
-        <v>1.445525</v>
+        <v>1.445815</v>
       </c>
       <c r="E50" s="7">
-        <v>433.86</v>
+        <v>433.95</v>
       </c>
       <c r="F50" s="7">
         <v>464.27</v>
@@ -2922,17 +3057,17 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B51" s="10">
-        <v>4186.7</v>
+        <v>4186.719</v>
       </c>
       <c r="C51" s="10">
         <v>43</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="10">
-        <v>6603.13</v>
+        <v>6600.49</v>
       </c>
       <c r="F51" s="10">
         <v>6997.08</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/СПЕДСТРОЙ ООД/СПЕДСТРОЙ ООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="160">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -504,9 +501,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -600,10 +597,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -898,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -911,13 +908,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -960,2034 +957,1902 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F2">
         <v>42.391</v>
       </c>
       <c r="G2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2">
+        <v>1.519</v>
+      </c>
+      <c r="I2" s="1">
+        <v>64.392</v>
+      </c>
+      <c r="J2">
+        <v>1.61</v>
+      </c>
+      <c r="K2" s="1">
+        <v>68.25</v>
+      </c>
+      <c r="L2" t="s">
         <v>69</v>
       </c>
-      <c r="H2">
-        <v>1.499</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.519</v>
-      </c>
-      <c r="J2">
-        <v>64.391929</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L2" s="1">
-        <v>68.24951</v>
-      </c>
-      <c r="M2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46219</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3">
         <v>300</v>
       </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H3">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I3" s="1">
-        <v>1.519</v>
+        <v>455.7</v>
       </c>
       <c r="J3">
-        <v>455.7</v>
+        <v>1.61</v>
       </c>
       <c r="K3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L3" s="1">
         <v>483</v>
       </c>
-      <c r="M3" t="s">
-        <v>71</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="L3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46219</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F4">
         <v>210.012</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H4">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I4" s="1">
-        <v>1.519</v>
+        <v>319.008</v>
       </c>
       <c r="J4">
-        <v>319.008228</v>
+        <v>1.61</v>
       </c>
       <c r="K4" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="L4" s="1">
-        <v>338.11932</v>
-      </c>
-      <c r="M4" t="s">
-        <v>72</v>
-      </c>
-      <c r="N4">
+        <v>338.119</v>
+      </c>
+      <c r="L4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M4">
         <v>232402</v>
       </c>
-      <c r="O4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46220</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5">
         <v>43.521</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H5">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I5" s="1">
-        <v>1.519</v>
+        <v>66.108</v>
       </c>
       <c r="J5">
-        <v>66.10839900000001</v>
+        <v>1.63</v>
       </c>
       <c r="K5" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L5" s="1">
-        <v>70.93922999999999</v>
-      </c>
-      <c r="M5" t="s">
-        <v>73</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>70.93899999999999</v>
+      </c>
+      <c r="L5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
         <v>46220</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F6">
         <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H6">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I6" s="1">
-        <v>1.519</v>
+        <v>53.165</v>
       </c>
       <c r="J6">
-        <v>53.165</v>
+        <v>1.63</v>
       </c>
       <c r="K6" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L6" s="1">
         <v>57.05</v>
       </c>
-      <c r="M6" t="s">
-        <v>74</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="L6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3">
         <v>46220</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F7">
         <v>240</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H7">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I7" s="1">
-        <v>1.519</v>
+        <v>364.56</v>
       </c>
       <c r="J7">
-        <v>364.56</v>
+        <v>1.63</v>
       </c>
       <c r="K7" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L7" s="1">
         <v>391.2</v>
       </c>
-      <c r="M7" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3">
         <v>46220</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8">
         <v>62.46</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H8">
-        <v>1.499</v>
+        <v>1.519</v>
       </c>
       <c r="I8" s="1">
-        <v>1.519</v>
+        <v>94.877</v>
       </c>
       <c r="J8">
-        <v>94.87674</v>
+        <v>1.63</v>
       </c>
       <c r="K8" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L8" s="1">
-        <v>101.8098</v>
-      </c>
-      <c r="M8" t="s">
-        <v>76</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+        <v>101.81</v>
+      </c>
+      <c r="L8" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3">
         <v>46221</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F9">
         <v>27.103</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H9">
-        <v>1.528</v>
+        <v>1.548</v>
       </c>
       <c r="I9" s="1">
-        <v>1.548</v>
+        <v>41.955</v>
       </c>
       <c r="J9">
-        <v>41.955444</v>
+        <v>1.65</v>
       </c>
       <c r="K9" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="L9" s="1">
-        <v>44.71995</v>
-      </c>
-      <c r="M9" t="s">
-        <v>77</v>
-      </c>
-      <c r="N9">
+        <v>44.72</v>
+      </c>
+      <c r="L9" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9">
         <v>232558</v>
       </c>
-      <c r="O9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3">
         <v>46222</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F10">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H10">
-        <v>1.528</v>
+        <v>1.548</v>
       </c>
       <c r="I10" s="1">
-        <v>1.548</v>
+        <v>30.96</v>
       </c>
       <c r="J10">
-        <v>30.96</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
         <v>33.6</v>
       </c>
-      <c r="M10" t="s">
-        <v>78</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3">
         <v>46223</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F11">
         <v>46.952</v>
       </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H11">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I11" s="1">
-        <v>1.566</v>
+        <v>73.527</v>
       </c>
       <c r="J11">
-        <v>73.526832</v>
+        <v>1.67</v>
       </c>
       <c r="K11" s="1">
-        <v>1.67</v>
-      </c>
-      <c r="L11" s="1">
-        <v>78.40984</v>
-      </c>
-      <c r="M11" t="s">
-        <v>79</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+        <v>78.41</v>
+      </c>
+      <c r="L11" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3">
         <v>46223</v>
       </c>
       <c r="B12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F12">
         <v>79.482</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H12">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I12" s="1">
-        <v>1.566</v>
+        <v>124.469</v>
       </c>
       <c r="J12">
-        <v>124.468812</v>
+        <v>1.68</v>
       </c>
       <c r="K12" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L12" s="1">
-        <v>133.52976</v>
-      </c>
-      <c r="M12" t="s">
-        <v>75</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>133.53</v>
+      </c>
+      <c r="L12" t="s">
+        <v>74</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3">
         <v>46223</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13">
         <v>150.012</v>
       </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H13">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I13" s="1">
-        <v>1.566</v>
+        <v>234.919</v>
       </c>
       <c r="J13">
-        <v>234.918792</v>
+        <v>1.68</v>
       </c>
       <c r="K13" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L13" s="1">
-        <v>252.02016</v>
-      </c>
-      <c r="M13" t="s">
-        <v>80</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>252.02</v>
+      </c>
+      <c r="L13" t="s">
+        <v>79</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3">
         <v>46223</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F14">
         <v>150</v>
       </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H14">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I14" s="1">
-        <v>1.566</v>
+        <v>234.9</v>
       </c>
       <c r="J14">
-        <v>234.9</v>
+        <v>1.68</v>
       </c>
       <c r="K14" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L14" s="1">
         <v>252</v>
       </c>
-      <c r="M14" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="L14" t="s">
+        <v>80</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3">
         <v>46223</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F15">
         <v>226.512</v>
       </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H15">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I15" s="1">
-        <v>1.566</v>
+        <v>354.718</v>
       </c>
       <c r="J15">
-        <v>354.717792</v>
+        <v>1.68</v>
       </c>
       <c r="K15" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L15" s="1">
-        <v>380.54016</v>
-      </c>
-      <c r="M15" t="s">
-        <v>82</v>
-      </c>
-      <c r="N15">
+        <v>380.54</v>
+      </c>
+      <c r="L15" t="s">
+        <v>81</v>
+      </c>
+      <c r="M15">
         <v>176492</v>
       </c>
-      <c r="O15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+      <c r="N15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3">
         <v>46223</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16">
         <v>213.03</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H16">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I16" s="1">
-        <v>1.566</v>
+        <v>333.605</v>
       </c>
       <c r="J16">
-        <v>333.60498</v>
+        <v>1.68</v>
       </c>
       <c r="K16" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L16" s="1">
-        <v>357.8904</v>
-      </c>
-      <c r="M16" t="s">
-        <v>83</v>
-      </c>
-      <c r="N16">
+        <v>357.89</v>
+      </c>
+      <c r="L16" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16">
         <v>100133</v>
       </c>
-      <c r="O16" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="N16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="3">
         <v>46223</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17">
         <v>35.708</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H17">
-        <v>1.546</v>
+        <v>1.566</v>
       </c>
       <c r="I17" s="1">
-        <v>1.566</v>
+        <v>55.919</v>
       </c>
       <c r="J17">
-        <v>55.918728</v>
+        <v>1.68</v>
       </c>
       <c r="K17" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L17" s="1">
-        <v>59.98944</v>
-      </c>
-      <c r="M17" t="s">
-        <v>84</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>59.989</v>
+      </c>
+      <c r="L17" t="s">
+        <v>83</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="3">
         <v>46223</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18">
         <v>36.451</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H18">
-        <v>1.389</v>
+        <v>1.419</v>
       </c>
       <c r="I18" s="1">
-        <v>1.419</v>
+        <v>51.724</v>
       </c>
       <c r="J18">
-        <v>51.723969</v>
+        <v>1.53</v>
       </c>
       <c r="K18" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L18" s="1">
-        <v>55.77003</v>
-      </c>
-      <c r="M18" t="s">
-        <v>85</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>55.77</v>
+      </c>
+      <c r="L18" t="s">
+        <v>84</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3">
         <v>46224</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F19">
         <v>235</v>
       </c>
       <c r="G19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H19">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I19" s="1">
-        <v>1.584</v>
+        <v>372.24</v>
       </c>
       <c r="J19">
-        <v>372.24</v>
+        <v>1.68</v>
       </c>
       <c r="K19" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L19" s="1">
         <v>394.8</v>
       </c>
-      <c r="M19" t="s">
-        <v>86</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="L19" t="s">
+        <v>85</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3">
         <v>46224</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F20">
         <v>83.351</v>
       </c>
       <c r="G20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H20">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I20" s="1">
-        <v>1.584</v>
+        <v>132.028</v>
       </c>
       <c r="J20">
-        <v>132.027984</v>
+        <v>1.68</v>
       </c>
       <c r="K20" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L20" s="1">
-        <v>140.02968</v>
-      </c>
-      <c r="M20" t="s">
-        <v>87</v>
-      </c>
-      <c r="N20">
+        <v>140.03</v>
+      </c>
+      <c r="L20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20">
         <v>233368</v>
       </c>
-      <c r="O20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="N20" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3">
         <v>46224</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F21">
         <v>150.012</v>
       </c>
       <c r="G21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I21" s="1">
-        <v>1.584</v>
+        <v>237.619</v>
       </c>
       <c r="J21">
-        <v>237.619008</v>
+        <v>1.68</v>
       </c>
       <c r="K21" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L21" s="1">
-        <v>252.02016</v>
-      </c>
-      <c r="M21" t="s">
-        <v>88</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>252.02</v>
+      </c>
+      <c r="L21" t="s">
+        <v>87</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="3">
         <v>46224</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E22" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F22">
         <v>34.202</v>
       </c>
       <c r="G22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H22">
-        <v>1.564</v>
+        <v>1.584</v>
       </c>
       <c r="I22" s="1">
-        <v>1.584</v>
+        <v>54.176</v>
       </c>
       <c r="J22">
-        <v>54.175968</v>
+        <v>1.68</v>
       </c>
       <c r="K22" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L22" s="1">
-        <v>57.45936</v>
-      </c>
-      <c r="M22" t="s">
-        <v>89</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>57.459</v>
+      </c>
+      <c r="L22" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3">
         <v>46225</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F23">
         <v>300.018</v>
       </c>
       <c r="G23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H23">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I23" s="1">
-        <v>1.608</v>
+        <v>482.429</v>
       </c>
       <c r="J23">
-        <v>482.428944</v>
+        <v>1.69</v>
       </c>
       <c r="K23" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L23" s="1">
-        <v>507.03042</v>
-      </c>
-      <c r="M23" t="s">
-        <v>90</v>
-      </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>507.03</v>
+      </c>
+      <c r="L23" t="s">
+        <v>89</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="3">
         <v>46225</v>
       </c>
       <c r="B24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F24">
         <v>64.69799999999999</v>
       </c>
       <c r="G24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H24">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I24" s="1">
-        <v>1.608</v>
+        <v>104.034</v>
       </c>
       <c r="J24">
-        <v>104.034384</v>
+        <v>1.69</v>
       </c>
       <c r="K24" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L24" s="1">
-        <v>109.33962</v>
-      </c>
-      <c r="M24" t="s">
-        <v>91</v>
-      </c>
-      <c r="N24">
+        <v>109.34</v>
+      </c>
+      <c r="L24" t="s">
+        <v>90</v>
+      </c>
+      <c r="M24">
         <v>243441</v>
       </c>
-      <c r="O24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+      <c r="N24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3">
         <v>46225</v>
       </c>
       <c r="B25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F25">
         <v>250</v>
       </c>
       <c r="G25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H25">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I25" s="1">
-        <v>1.608</v>
+        <v>402</v>
       </c>
       <c r="J25">
-        <v>402</v>
+        <v>1.69</v>
       </c>
       <c r="K25" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L25" s="1">
         <v>422.5</v>
       </c>
-      <c r="M25" t="s">
-        <v>92</v>
-      </c>
-      <c r="N25">
+      <c r="L25" t="s">
+        <v>91</v>
+      </c>
+      <c r="M25">
         <v>194160</v>
       </c>
-      <c r="O25" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+      <c r="N25" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="3">
         <v>46226</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F26">
         <v>58.159</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H26">
-        <v>1.588</v>
+        <v>1.608</v>
       </c>
       <c r="I26" s="1">
-        <v>1.608</v>
+        <v>93.52</v>
       </c>
       <c r="J26">
-        <v>93.519672</v>
+        <v>1.7</v>
       </c>
       <c r="K26" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L26" s="1">
-        <v>98.8703</v>
-      </c>
-      <c r="M26" t="s">
-        <v>93</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+        <v>98.87</v>
+      </c>
+      <c r="L26" t="s">
+        <v>92</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="3">
         <v>46226</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27">
         <v>47.331</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H27">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I27" s="1">
-        <v>1.431</v>
+        <v>67.73099999999999</v>
       </c>
       <c r="J27">
-        <v>67.730661</v>
+        <v>1.54</v>
       </c>
       <c r="K27" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L27" s="1">
-        <v>72.88974</v>
-      </c>
-      <c r="M27" t="s">
-        <v>94</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+        <v>72.89</v>
+      </c>
+      <c r="L27" t="s">
+        <v>93</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="3">
         <v>46226</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F28">
         <v>42.5</v>
       </c>
       <c r="G28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H28">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I28" s="1">
-        <v>1.431</v>
+        <v>60.818</v>
       </c>
       <c r="J28">
-        <v>60.8175</v>
+        <v>1.54</v>
       </c>
       <c r="K28" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L28" s="1">
         <v>65.45</v>
       </c>
-      <c r="M28" t="s">
-        <v>95</v>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+      <c r="L28" t="s">
+        <v>94</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="3">
         <v>46227</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E29" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29">
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H29">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I29" s="1">
-        <v>1.431</v>
+        <v>28.62</v>
       </c>
       <c r="J29">
-        <v>28.62</v>
+        <v>1.54</v>
       </c>
       <c r="K29" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L29" s="1">
         <v>30.8</v>
       </c>
-      <c r="M29" t="s">
-        <v>96</v>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+      <c r="L29" t="s">
+        <v>95</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="3">
         <v>46227</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F30">
         <v>45</v>
       </c>
       <c r="G30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H30">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I30" s="1">
-        <v>1.639</v>
+        <v>73.755</v>
       </c>
       <c r="J30">
-        <v>73.755</v>
+        <v>1.72</v>
       </c>
       <c r="K30" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L30" s="1">
         <v>77.40000000000001</v>
       </c>
-      <c r="M30" t="s">
-        <v>97</v>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+      <c r="L30" t="s">
+        <v>96</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="3">
         <v>46227</v>
       </c>
       <c r="B31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F31">
         <v>54.029</v>
       </c>
       <c r="G31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H31">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I31" s="1">
-        <v>1.639</v>
+        <v>88.554</v>
       </c>
       <c r="J31">
-        <v>88.55353100000001</v>
+        <v>1.7</v>
       </c>
       <c r="K31" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="L31" s="1">
-        <v>91.8493</v>
-      </c>
-      <c r="M31" t="s">
-        <v>98</v>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+        <v>91.849</v>
+      </c>
+      <c r="L31" t="s">
+        <v>97</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="3">
         <v>46227</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F32">
         <v>67</v>
       </c>
       <c r="G32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H32">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I32" s="1">
-        <v>1.639</v>
+        <v>109.813</v>
       </c>
       <c r="J32">
-        <v>109.813</v>
+        <v>1.72</v>
       </c>
       <c r="K32" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L32" s="1">
         <v>115.24</v>
       </c>
-      <c r="M32" t="s">
-        <v>99</v>
-      </c>
-      <c r="N32">
+      <c r="L32" t="s">
+        <v>98</v>
+      </c>
+      <c r="M32">
         <v>500995</v>
       </c>
-      <c r="O32" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15">
+      <c r="N32" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="3">
         <v>46228</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33">
         <v>47.82</v>
       </c>
       <c r="G33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H33">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I33" s="1">
-        <v>1.639</v>
+        <v>78.377</v>
       </c>
       <c r="J33">
-        <v>78.37698</v>
+        <v>1.72</v>
       </c>
       <c r="K33" s="1">
-        <v>1.72</v>
-      </c>
-      <c r="L33" s="1">
-        <v>82.2504</v>
-      </c>
-      <c r="M33" t="s">
-        <v>100</v>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15">
+        <v>82.25</v>
+      </c>
+      <c r="L33" t="s">
+        <v>99</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" s="3">
         <v>46228</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F34">
         <v>35.483</v>
       </c>
       <c r="G34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H34">
-        <v>1.619</v>
+        <v>1.639</v>
       </c>
       <c r="I34" s="1">
-        <v>1.639</v>
+        <v>58.157</v>
       </c>
       <c r="J34">
-        <v>58.156637</v>
+        <v>1.74</v>
       </c>
       <c r="K34" s="1">
-        <v>1.74</v>
-      </c>
-      <c r="L34" s="1">
-        <v>61.74042</v>
-      </c>
-      <c r="M34" t="s">
-        <v>101</v>
-      </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
-      <c r="O34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15">
+        <v>61.74</v>
+      </c>
+      <c r="L34" t="s">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" s="3">
         <v>46229</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35">
         <v>45</v>
       </c>
       <c r="G35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H35">
-        <v>1.401</v>
+        <v>1.431</v>
       </c>
       <c r="I35" s="1">
-        <v>1.431</v>
+        <v>64.395</v>
       </c>
       <c r="J35">
-        <v>64.395</v>
+        <v>1.56</v>
       </c>
       <c r="K35" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L35" s="1">
         <v>70.2</v>
       </c>
-      <c r="M35" t="s">
-        <v>102</v>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15">
+      <c r="L35" t="s">
+        <v>101</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" s="3">
         <v>46231</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F36">
         <v>100</v>
       </c>
       <c r="G36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H36">
-        <v>1.653</v>
+        <v>1.673</v>
       </c>
       <c r="I36" s="1">
-        <v>1.673</v>
+        <v>167.3</v>
       </c>
       <c r="J36">
-        <v>167.3</v>
+        <v>1.75</v>
       </c>
       <c r="K36" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L36" s="1">
         <v>175</v>
       </c>
-      <c r="M36" t="s">
-        <v>103</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15">
+      <c r="L36" t="s">
+        <v>102</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" s="3">
         <v>46231</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F37">
         <v>207.72</v>
       </c>
       <c r="G37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H37">
-        <v>1.653</v>
+        <v>1.673</v>
       </c>
       <c r="I37" s="1">
-        <v>1.673</v>
+        <v>347.516</v>
       </c>
       <c r="J37">
-        <v>347.51556</v>
+        <v>1.75</v>
       </c>
       <c r="K37" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L37" s="1">
         <v>363.51</v>
       </c>
-      <c r="M37" t="s">
-        <v>104</v>
-      </c>
-      <c r="N37">
+      <c r="L37" t="s">
+        <v>103</v>
+      </c>
+      <c r="M37">
         <v>100517</v>
       </c>
-      <c r="O37" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15">
+      <c r="N37" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" s="3">
         <v>46231</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38">
         <v>42.641</v>
       </c>
       <c r="G38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H38">
-        <v>1.441</v>
+        <v>1.471</v>
       </c>
       <c r="I38" s="1">
-        <v>1.471</v>
+        <v>62.725</v>
       </c>
       <c r="J38">
-        <v>62.724911</v>
+        <v>1.56</v>
       </c>
       <c r="K38" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L38" s="1">
-        <v>66.51996</v>
-      </c>
-      <c r="M38" t="s">
-        <v>105</v>
-      </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15">
+        <v>66.52</v>
+      </c>
+      <c r="L38" t="s">
+        <v>104</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" s="3">
         <v>46232</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F39">
         <v>45</v>
       </c>
       <c r="G39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H39">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I39" s="1">
-        <v>1.694</v>
+        <v>76.23</v>
       </c>
       <c r="J39">
-        <v>76.23</v>
+        <v>1.75</v>
       </c>
       <c r="K39" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L39" s="1">
         <v>78.75</v>
       </c>
-      <c r="M39" t="s">
-        <v>106</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="O39" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15">
+      <c r="L39" t="s">
+        <v>105</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" s="3">
         <v>46232</v>
       </c>
       <c r="B40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F40">
         <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H40">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I40" s="1">
-        <v>1.694</v>
+        <v>101.64</v>
       </c>
       <c r="J40">
-        <v>101.64</v>
+        <v>1.75</v>
       </c>
       <c r="K40" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L40" s="1">
         <v>105</v>
       </c>
-      <c r="M40" t="s">
-        <v>107</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15">
+      <c r="L40" t="s">
+        <v>106</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" s="3">
         <v>46232</v>
       </c>
       <c r="B41" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41">
         <v>66.21899999999999</v>
       </c>
       <c r="G41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H41">
-        <v>1.449</v>
+        <v>1.479</v>
       </c>
       <c r="I41" s="1">
-        <v>1.479</v>
+        <v>97.938</v>
       </c>
       <c r="J41">
-        <v>97.937901</v>
+        <v>1.55</v>
       </c>
       <c r="K41" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L41" s="1">
-        <v>102.63945</v>
-      </c>
-      <c r="M41" t="s">
-        <v>108</v>
-      </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15">
+        <v>102.639</v>
+      </c>
+      <c r="L41" t="s">
+        <v>107</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" s="3">
         <v>46233</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F42">
         <v>57.398</v>
       </c>
       <c r="G42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H42">
-        <v>1.674</v>
+        <v>1.694</v>
       </c>
       <c r="I42" s="1">
-        <v>1.694</v>
+        <v>97.232</v>
       </c>
       <c r="J42">
-        <v>97.232212</v>
+        <v>1.76</v>
       </c>
       <c r="K42" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L42" s="1">
-        <v>101.02048</v>
-      </c>
-      <c r="M42" t="s">
-        <v>109</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15">
+        <v>101.02</v>
+      </c>
+      <c r="L42" t="s">
+        <v>108</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" s="3">
         <v>46234</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F43">
         <v>39.232</v>
       </c>
       <c r="G43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H43">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I43" s="1">
-        <v>1.709</v>
+        <v>67.047</v>
       </c>
       <c r="J43">
-        <v>67.047488</v>
+        <v>1.77</v>
       </c>
       <c r="K43" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L43" s="1">
-        <v>69.44064</v>
-      </c>
-      <c r="M43" t="s">
-        <v>110</v>
-      </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15">
+        <v>69.441</v>
+      </c>
+      <c r="L43" t="s">
+        <v>109</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" s="3">
         <v>46234</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F44">
         <v>70.27200000000001</v>
       </c>
       <c r="G44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H44">
-        <v>1.689</v>
+        <v>1.709</v>
       </c>
       <c r="I44" s="1">
-        <v>1.709</v>
+        <v>120.095</v>
       </c>
       <c r="J44">
-        <v>120.094848</v>
+        <v>1.8</v>
       </c>
       <c r="K44" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L44" s="1">
-        <v>126.4896</v>
-      </c>
-      <c r="M44" t="s">
-        <v>111</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
+        <v>126.49</v>
+      </c>
+      <c r="L44" t="s">
+        <v>110</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="A47" s="4" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -2995,69 +2860,69 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:14">
       <c r="A48" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B48" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="C48" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="D48" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>159</v>
-      </c>
       <c r="E48" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" s="7">
         <v>3886.577</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="8">
         <v>36</v>
       </c>
       <c r="D49" s="8">
-        <v>1.586626</v>
-      </c>
-      <c r="E49" s="7">
-        <v>6166.54</v>
-      </c>
-      <c r="F49" s="7">
-        <v>6532.81</v>
+        <v>1.587</v>
+      </c>
+      <c r="E49" s="8">
+        <v>6166.544</v>
+      </c>
+      <c r="F49" s="8">
+        <v>6532.806</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" s="7">
         <v>300.142</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="8">
         <v>7</v>
       </c>
       <c r="D50" s="8">
-        <v>1.445815</v>
-      </c>
-      <c r="E50" s="7">
-        <v>433.95</v>
-      </c>
-      <c r="F50" s="7">
-        <v>464.27</v>
+        <v>1.446</v>
+      </c>
+      <c r="E50" s="8">
+        <v>433.951</v>
+      </c>
+      <c r="F50" s="8">
+        <v>464.269</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B51" s="10">
         <v>4186.719</v>
@@ -3067,10 +2932,10 @@
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="10">
-        <v>6600.49</v>
+        <v>6600.495</v>
       </c>
       <c r="F51" s="10">
-        <v>6997.08</v>
+        <v>6997.075</v>
       </c>
     </row>
   </sheetData>
